--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.155.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.155.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -839,7 +839,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.155.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.155.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="41" customWidth="1" min="14" max="14"/>
     <col width="40" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -605,16 +605,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: to be made in â€œThe Solicitor's and</t>
+          <t>L144: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP :: 。 number of</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: / â€” / same, or they may be forwarded by special messenger, in</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ORDERS OF JANUARY 1851.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]ORDERS OF JANUARY 1851.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L22: isolated marker/symbol line :: 148</t>
@@ -630,7 +634,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L99: line starts with punctuation glued to text :: .number of</t>
+          <t>L85: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • The copy</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -666,14 +670,10 @@
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr"/>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>L127: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: nat can become Ã© necessary in the con-</t>
-        </is>
-      </c>
+      <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L11: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: Registrars. â€¢solicitors residing elsewhere than in the county in which</t>
+          <t>L11: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: Registrars. •solicitors residing elsewhere than in the county in which</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -687,7 +687,11 @@
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr"/>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L99: line starts with punctuation glued to text :: .number of</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -721,14 +725,10 @@
         </is>
       </c>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L144: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ã€‚ number of</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L85: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ The copy</t>
+          <t>L85: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • The copy</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -758,7 +758,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -965,7 +965,7 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
